--- a/data/trans_camb/P1412-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1412-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,59</t>
+          <t>-0,7; 1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,18</t>
+          <t>-0,53; 2,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,87</t>
+          <t>-1,26; 0,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,53</t>
+          <t>-1,23; 0,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,8</t>
+          <t>-0,72; 0,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,95</t>
+          <t>-0,57; 0,97</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-21,39%</t>
+          <t>-16,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 180,17</t>
+          <t>-40,02; 179,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 246,47</t>
+          <t>-34,99; 260,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 75,46</t>
+          <t>-61,54; 78,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,45; 54,34</t>
+          <t>-56,81; 54,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 64,97</t>
+          <t>-39,92; 72,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 84,62</t>
+          <t>-31,52; 83,07</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,17 +764,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,32</t>
+          <t>-0,53; 0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,49</t>
+          <t>-0,39; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,41</t>
+          <t>-0,13; 0,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,42</t>
+          <t>0,01; 0,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,28</t>
+          <t>-0,28; 0,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,37</t>
+          <t>-0,09; 0,48</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164,63%</t>
+          <t>231,03%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,25; 128,15</t>
+          <t>-72,82; 161,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 178,09</t>
+          <t>-53,74; 223,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,68; —</t>
+          <t>-35,36; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,47; 170,82</t>
+          <t>-62,86; 176,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 218,24</t>
+          <t>-23,66; 268,84</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,43</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,17; 1,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,78</t>
+          <t>0,43; 1,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,38</t>
+          <t>-0,73; 0,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,37</t>
+          <t>-0,92; 0,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,92</t>
+          <t>-0,08; 1,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,85</t>
+          <t>0,07; 0,83</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-18,42%</t>
+          <t>-24,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>403,1%</t>
+          <t>381,06%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,53</t>
+          <t>-0,32; 0,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,63</t>
+          <t>-0,13; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,24</t>
+          <t>-0,52; 0,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,09</t>
+          <t>-0,53; 0,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,24</t>
+          <t>-0,3; 0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,25</t>
+          <t>-0,22; 0,34</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-29,6%</t>
+          <t>-19,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 118,39</t>
+          <t>-37,64; 113,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 135,34</t>
+          <t>-18,85; 150,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,91; 45,69</t>
+          <t>-60,31; 48,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 19,56</t>
+          <t>-53,0; 42,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,4; 48,04</t>
+          <t>-36,41; 47,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 47,86</t>
+          <t>-26,82; 63,5</t>
         </is>
       </c>
     </row>
